--- a/asset-forge/products/pack_airbnb_sk.xlsx
+++ b/asset-forge/products/pack_airbnb_sk.xlsx
@@ -376,10 +376,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="18" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="19" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="18" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1574,36 +1574,36 @@
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="28" t="inlineStr">
         <is>
-          <t>KONCOVÁ HOTOVOSŤ  ↗</t>
+          <t>TRŽBY VS PLÁN  ↗</t>
         </is>
       </c>
       <c r="D11" s="29" t="n"/>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>PRIEMERNÁ MARŽA DOPLNKOV  ↗</t>
+          <t>KONCOVÁ HOTOVOSŤ  ↗</t>
         </is>
       </c>
       <c r="H11" s="29" t="n"/>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>HODNOTA STRÁT (SPOTREBA)  ↗</t>
+          <t>PRIEMERNÁ MARŽA DOPLNKOV  ↗</t>
         </is>
       </c>
       <c r="L11" s="29" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="30">
+        <f>IFERROR('03 · Cash flow'!Q13,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="29" t="n"/>
+      <c r="F12" s="31">
         <f>IFERROR('03 · Cash flow'!N29,0)</f>
         <v/>
       </c>
-      <c r="D12" s="29" t="n"/>
-      <c r="F12" s="36">
+      <c r="H12" s="29" t="n"/>
+      <c r="J12" s="36">
         <f>IFERROR('04 · Marža doplnkov'!H30,0)</f>
-        <v/>
-      </c>
-      <c r="H12" s="29" t="n"/>
-      <c r="J12" s="32">
-        <f>IFERROR('05 · Spotreba a straty'!I27,0)</f>
         <v/>
       </c>
       <c r="L12" s="29" t="n"/>
@@ -1624,26 +1624,43 @@
       <c r="B15" s="23" t="inlineStr"/>
       <c r="C15" s="24" t="n"/>
       <c r="D15" s="25" t="n"/>
+      <c r="F15" s="26" t="inlineStr"/>
+      <c r="G15" s="24" t="n"/>
+      <c r="H15" s="25" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="28" t="inlineStr">
         <is>
+          <t>HODNOTA STRÁT (SPOTREBA)  ↗</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="n"/>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
           <t>PODIEL NÁKLADOV NA UPRATOVANIE  ↗</t>
         </is>
       </c>
-      <c r="D16" s="29" t="n"/>
+      <c r="H16" s="29" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="37">
+      <c r="B17" s="30">
+        <f>IFERROR('05 · Spotreba a straty'!I27,0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="29" t="n"/>
+      <c r="F17" s="37">
         <f>IFERROR('06 · Zmeny'!I31,0)</f>
         <v/>
       </c>
-      <c r="D17" s="29" t="n"/>
+      <c r="H17" s="29" t="n"/>
     </row>
     <row r="18" ht="14" customHeight="1">
       <c r="B18" s="33" t="n"/>
       <c r="C18" s="34" t="n"/>
       <c r="D18" s="35" t="n"/>
+      <c r="F18" s="33" t="n"/>
+      <c r="G18" s="34" t="n"/>
+      <c r="H18" s="35" t="n"/>
     </row>
     <row r="19"/>
     <row r="20" ht="24" customHeight="1">
@@ -1768,7 +1785,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="34">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="B26:L26"/>
@@ -1790,15 +1807,18 @@
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B28:L28"/>
+    <mergeCell ref="F17:H18"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="J7:L8"/>
+    <mergeCell ref="F16:H16"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="J10:L10"/>
     <mergeCell ref="B24:L24"/>
     <mergeCell ref="B20:L20"/>
+    <mergeCell ref="F15:H15"/>
     <mergeCell ref="J12:L13"/>
   </mergeCells>
   <conditionalFormatting sqref="J7">
@@ -1806,7 +1826,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
+  <conditionalFormatting sqref="F17">
     <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="0">
       <formula>0.35</formula>
     </cfRule>
@@ -1819,6 +1839,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
